--- a/data/trans_orig/IP22B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22B-Provincia-trans_orig.xlsx
@@ -994,47 +994,47 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>28,44%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>638</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5421</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>30,45%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14877</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15994</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>19878</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,86%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>13727</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>25694</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>30296</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>42601</t>
+          <t>42782</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>20140</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>30964</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -6415,12 +6415,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6465,12 +6465,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6500,12 +6500,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>47412</t>
+          <t>47922</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>65970</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>72860</t>
+          <t>72309</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>105949</t>
+          <t>106784</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>132699</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>57131</t>
+          <t>57208</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>75664</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>96142</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>140023</t>
+          <t>138737</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>166567</t>
+          <t>164741</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12672</t>
+          <t>12897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>30210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7987,12 +7987,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22846</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36667</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25068</t>
+          <t>24921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>31245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18029</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29527</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,43%</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9527,12 +9527,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9562,12 +9562,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9577,12 +9577,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -9605,12 +9605,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9640,12 +9640,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>20184</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9655,12 +9655,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -10174,12 +10174,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10209,12 +10209,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10244,12 +10244,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>23141</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10259,12 +10259,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -10287,12 +10287,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -10856,12 +10856,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -10969,12 +10969,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>15319</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>25689</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -11425,12 +11425,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -11538,12 +11538,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11553,12 +11553,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>28961</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11588,12 +11588,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>38435</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -11651,12 +11651,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16526</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11666,12 +11666,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11701,12 +11701,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>31341</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>45437</t>
+          <t>45886</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -12220,12 +12220,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12235,12 +12235,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12305,12 +12305,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -12333,12 +12333,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12383,12 +12383,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12418,12 +12418,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -12676,12 +12676,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12691,12 +12691,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12711,12 +12711,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12746,12 +12746,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12761,12 +12761,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12839,12 +12839,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12859,12 +12859,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>57427</t>
+          <t>57040</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>77787</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12917,12 +12917,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>77679</t>
+          <t>78319</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>101451</t>
+          <t>102156</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12952,12 +12952,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12972,12 +12972,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>140872</t>
+          <t>140726</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>172315</t>
+          <t>172175</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12987,12 +12987,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -13015,12 +13015,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>80552</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>100950</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13030,12 +13030,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13050,12 +13050,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>95974</t>
+          <t>96282</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>120723</t>
+          <t>120253</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13065,12 +13065,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13085,12 +13085,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>181853</t>
+          <t>183464</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>215366</t>
+          <t>216016</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13100,12 +13100,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -13707,12 +13707,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13722,12 +13722,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13777,12 +13777,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -13820,12 +13820,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13855,12 +13855,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17886</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -13933,12 +13933,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13983,12 +13983,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>20685</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31615</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14218,7 +14218,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -14394,7 +14394,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -14502,12 +14502,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14537,12 +14537,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>16894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -14615,12 +14615,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>18555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20086</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32565</t>
+          <t>31879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15367,12 +15367,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -15866,12 +15866,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15881,12 +15881,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>12798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15916,12 +15916,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15936,12 +15936,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15951,12 +15951,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -15979,12 +15979,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16029,12 +16029,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16064,12 +16064,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16563,12 +16563,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16633,12 +16633,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -16661,12 +16661,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16676,12 +16676,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16731,12 +16731,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16746,12 +16746,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -17230,12 +17230,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17245,12 +17245,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17285,7 +17285,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -17343,12 +17343,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17358,12 +17358,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -17428,7 +17428,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -17686,12 +17686,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17701,12 +17701,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17756,12 +17756,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17771,12 +17771,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -17804,7 +17804,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -18025,12 +18025,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18040,12 +18040,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -18095,12 +18095,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17834</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18110,12 +18110,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -18403,12 +18403,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18418,12 +18418,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18438,12 +18438,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18453,12 +18453,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -18481,12 +18481,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>742</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18496,12 +18496,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18516,12 +18516,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>555</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18531,12 +18531,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18551,12 +18551,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -18594,12 +18594,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18609,12 +18609,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18629,12 +18629,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18644,12 +18644,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -18707,12 +18707,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18722,12 +18722,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18742,12 +18742,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18757,12 +18757,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18777,12 +18777,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18792,12 +18792,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -19050,12 +19050,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19085,12 +19085,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19100,12 +19100,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19120,12 +19120,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19135,12 +19135,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -19163,12 +19163,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19178,12 +19178,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19198,12 +19198,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19213,12 +19213,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19233,12 +19233,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19248,12 +19248,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -19276,12 +19276,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>51922</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19291,12 +19291,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19311,12 +19311,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19326,12 +19326,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19346,12 +19346,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>65117</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>88065</t>
+          <t>87536</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19361,12 +19361,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -19389,12 +19389,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>59300</t>
+          <t>59314</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>76718</t>
+          <t>76846</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19404,12 +19404,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19424,12 +19424,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>69287</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>86851</t>
+          <t>87106</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19439,12 +19439,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19459,12 +19459,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>134822</t>
+          <t>134029</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>158713</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19474,12 +19474,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -19968,12 +19968,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -19983,12 +19983,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -20003,12 +20003,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -20018,12 +20018,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -20038,12 +20038,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -20053,12 +20053,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -20194,12 +20194,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -20209,12 +20209,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -20229,12 +20229,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -20244,12 +20244,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -20264,12 +20264,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -20279,12 +20279,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -20307,12 +20307,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22566</t>
+          <t>22439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -20322,12 +20322,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -20342,12 +20342,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -20357,12 +20357,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -20377,12 +20377,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24717</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>37042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -20392,12 +20392,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -20655,7 +20655,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -20705,7 +20705,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -20720,12 +20720,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -20735,12 +20735,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -20768,7 +20768,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -20876,12 +20876,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -20891,12 +20891,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -20911,12 +20911,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -20946,12 +20946,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -20961,12 +20961,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -20989,12 +20989,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -21004,12 +21004,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -21024,12 +21024,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -21039,12 +21039,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -21059,12 +21059,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26011</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -21352,7 +21352,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -21485,7 +21485,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -21535,7 +21535,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -21558,12 +21558,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -21573,12 +21573,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -21593,12 +21593,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -21608,12 +21608,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -21628,12 +21628,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -21643,12 +21643,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -21686,12 +21686,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -21706,12 +21706,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -21721,12 +21721,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -21741,12 +21741,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -21756,12 +21756,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -22014,12 +22014,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -22029,12 +22029,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -22084,12 +22084,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -22099,12 +22099,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -22127,12 +22127,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>449</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -22142,12 +22142,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -22197,12 +22197,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>478</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -22212,12 +22212,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -22275,12 +22275,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -22290,12 +22290,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -22310,12 +22310,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -22325,12 +22325,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -22353,12 +22353,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -22368,12 +22368,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -22388,12 +22388,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -22403,12 +22403,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -22423,12 +22423,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19566</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -22438,12 +22438,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -22849,7 +22849,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -23531,7 +23531,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -23566,7 +23566,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -23581,7 +23581,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -23604,12 +23604,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -23619,12 +23619,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -23639,12 +23639,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -23654,12 +23654,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -23674,12 +23674,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -23689,12 +23689,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -23717,12 +23717,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -23732,12 +23732,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -23752,12 +23752,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -23767,12 +23767,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -24130,12 +24130,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -24145,12 +24145,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -24173,12 +24173,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -24188,12 +24188,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -24208,12 +24208,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -24243,12 +24243,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -24258,12 +24258,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -24286,12 +24286,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -24301,12 +24301,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -24321,12 +24321,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -24336,12 +24336,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -24356,12 +24356,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12360</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -24371,12 +24371,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -24399,12 +24399,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21462</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -24414,12 +24414,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -24434,12 +24434,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>32611</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -24449,12 +24449,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -24469,12 +24469,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>38317</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>51644</t>
+          <t>51649</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -24484,12 +24484,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -24860,7 +24860,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -24875,7 +24875,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -24895,7 +24895,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -24910,7 +24910,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -24930,7 +24930,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -24945,7 +24945,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -24968,12 +24968,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -24983,12 +24983,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -25023,7 +25023,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -25038,12 +25038,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>947</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -25081,12 +25081,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>381</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -25096,12 +25096,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -25116,12 +25116,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -25131,12 +25131,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -25151,12 +25151,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -25166,12 +25166,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -25424,12 +25424,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -25459,12 +25459,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -25474,12 +25474,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -25494,12 +25494,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -25509,12 +25509,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -25537,12 +25537,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -25552,12 +25552,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -25572,12 +25572,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -25587,12 +25587,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -25607,12 +25607,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -25622,12 +25622,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -25650,12 +25650,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>25984</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -25665,12 +25665,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -25685,12 +25685,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>37093</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -25700,12 +25700,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -25720,12 +25720,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -25735,12 +25735,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -25763,12 +25763,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>62380</t>
+          <t>61777</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>78649</t>
+          <t>78912</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -25778,12 +25778,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>84973</t>
+          <t>84357</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -25813,12 +25813,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -25833,12 +25833,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>131869</t>
+          <t>131681</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>156877</t>
+          <t>157602</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -25848,12 +25848,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
